--- a/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
+++ b/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
@@ -948,7 +948,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Электроснабжение: техприсоединение ≥ 60 кВт, ВРУ, ввод</t>
+          <t>Электроснабжение: техприсоединение 50 кВт, ВРУ, ввод</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">

--- a/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
+++ b/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -517,14 +517,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Оставшиеся проекты (ЭОМ, СС, ГП, наружные сети, КД6) и проверка инженером</t>
+          <t>Оставшиеся проекты (ГП, наружные сети по ТУ, КД6, проект ГСВ) и проверка инженером</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="D4" s="6">
         <f>(B4+C4)/2</f>
@@ -776,33 +776,33 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Инженерные системы</t>
+          <t>Инженерные системы (по разделам РД, см. «Бюджет по разделам РД»)</t>
         </is>
       </c>
       <c r="B19" s="4">
-        <f>SUM(B20:B34)</f>
+        <f>SUM(B20:B28)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>SUM(C20:C34)</f>
+        <f>SUM(C20:C28)</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>SUM(D20:D34)</f>
+        <f>SUM(D20:D28)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Вентиляция и кондиционирование (291-ОВК), под ключ</t>
+          <t>291-ОВК Вентиляция и кондиционирование</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4550</v>
+        <v>4840</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>7600</v>
+        <v>8060</v>
       </c>
       <c r="D20" s="6">
         <f>(B20+C20)/2</f>
@@ -812,14 +812,14 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Отопление и котельная, этап 1: пеллетный + электрокотёл, буфер, бойлер, обвязка</t>
+          <t>291-ОВ Отопление, тёплые полы, котельная</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1600</v>
+        <v>5730</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3100</v>
+        <v>10900</v>
       </c>
       <c r="D21" s="6">
         <f>(B21+C21)/2</f>
@@ -829,14 +829,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Тёплые полы (≈ 400 м²) и внутрипольные конвекторы/радиаторы</t>
+          <t>291-ВК Водоснабжение и канализация (внутренние)</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2200</v>
+        <v>1030</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>3700</v>
+        <v>2050</v>
       </c>
       <c r="D22" s="6">
         <f>(B22+C22)/2</f>
@@ -846,14 +846,14 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Дымоход, огнезащита котельной, пеллетный склад с подачей</t>
+          <t>291-ЭОМ Электрооборудование и освещение</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>500</v>
+        <v>2620</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1100</v>
+        <v>6210</v>
       </c>
       <c r="D23" s="6">
         <f>(B23+C23)/2</f>
@@ -863,14 +863,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Газ, этап 2: подключение, проект ГСВ, конденсационный котёл с монтажом</t>
+          <t>291-СС Слаботочные системы</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>450</v>
+        <v>860</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1100</v>
+        <v>2140</v>
       </c>
       <c r="D24" s="6">
         <f>(B24+C24)/2</f>
@@ -880,14 +880,14 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Водопровод и канализация внутренние (291-ВК) с монтажом</t>
+          <t>291-МЗ.ПС Молниезащита, заземление, пожарная сигнализация</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>900</v>
+        <v>520</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1500</v>
+        <v>1040</v>
       </c>
       <c r="D25" s="6">
         <f>(B25+C25)/2</f>
@@ -897,14 +897,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Сантехнические приборы (по дизайн-проекту)</t>
+          <t>291-НС Наружные сети (предварительно)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>3500</v>
+        <v>2470</v>
       </c>
       <c r="D26" s="6">
         <f>(B26+C26)/2</f>
@@ -914,14 +914,14 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Защита от протечек, водоподготовка</t>
+          <t>Газ, этап 2: конденсационный котёл, газопровод по участку, проект ГСВ, датчик метана</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>250</v>
+        <v>1400</v>
       </c>
       <c r="D27" s="6">
         <f>(B27+C27)/2</f>
@@ -931,14 +931,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Подключение к центральным водопроводу и канализации (ТУ, наружные сети)</t>
+          <t>Сантехнические приборы (по дизайн-проекту)</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="D28" s="6">
         <f>(B28+C28)/2</f>
@@ -946,33 +946,35 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Электроснабжение: техприсоединение 50 кВт, ВРУ, ввод</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D29" s="6">
-        <f>(B29+C29)/2</f>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Отделка и участок</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>SUM(B30:B32)</f>
+        <v/>
+      </c>
+      <c r="C29" s="4">
+        <f>SUM(C30:C32)</f>
+        <v/>
+      </c>
+      <c r="D29" s="4">
+        <f>SUM(D30:D32)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ЭОМ внутренние (щиты, кабели, розетки, выключатели)</t>
+          <t>Внутренняя отделка (полы, плитка, покраска, потолки, двери)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1600</v>
+        <v>8800</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2800</v>
+        <v>19500</v>
       </c>
       <c r="D30" s="6">
         <f>(B30+C30)/2</f>
@@ -982,14 +984,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Светильники</t>
+          <t>Благоустройство: отмостка, дорожки, озеленение (ливнёвка — в 291-НС)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="D31" s="6">
         <f>(B31+C31)/2</f>
@@ -999,14 +1001,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Слаботочные системы, видеонаблюдение, «умный дом» (база)</t>
+          <t>Временные сооружения, вывоз мусора, охрана</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
         <v>400</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="D32" s="6">
         <f>(B32+C32)/2</f>
@@ -1016,142 +1018,38 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Молниезащита и заземление (291-МЗ.ПС)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>450</v>
+          <t>Непредвиденные расходы 7 %</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>ROUND(0.07*(B2+B6+B9+B19+B29),-1)</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>ROUND(0.07*(C2+C6+C9+C19+C29),-1)</f>
+        <v/>
       </c>
       <c r="D33" s="6">
-        <f>(B33+C33)/2</f>
+        <f>ROUND(0.07*(D2+D6+D9+D19+D29),-1)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Пожарная сигнализация (291-МЗ.ПС)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="D34" s="6">
-        <f>(B34+C34)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Отделка и участок</t>
-        </is>
-      </c>
-      <c r="B35" s="4">
-        <f>SUM(B36:B38)</f>
-        <v/>
-      </c>
-      <c r="C35" s="4">
-        <f>SUM(C36:C38)</f>
-        <v/>
-      </c>
-      <c r="D35" s="4">
-        <f>SUM(D36:D38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Внутренняя отделка (полы, плитка, покраска, потолки, двери)</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>8800</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>19500</v>
-      </c>
-      <c r="D36" s="6">
-        <f>(B36+C36)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Благоустройство: отмостка, дорожки, ливнёвка, озеленение</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D37" s="6">
-        <f>(B37+C37)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Временные сооружения, вывоз мусора, охрана</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>800</v>
-      </c>
-      <c r="D38" s="6">
-        <f>(B38+C38)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Непредвиденные расходы 7 %</t>
-        </is>
-      </c>
-      <c r="B39" s="6">
-        <f>ROUND(0.07*(B2+B6+B9+B19+B35),-1)</f>
-        <v/>
-      </c>
-      <c r="C39" s="6">
-        <f>ROUND(0.07*(C2+C6+C9+C19+C35),-1)</f>
-        <v/>
-      </c>
-      <c r="D39" s="6">
-        <f>ROUND(0.07*(D2+D6+D9+D19+D35),-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B40" s="4">
-        <f>B2+B6+B9+B19+B35+B39</f>
-        <v/>
-      </c>
-      <c r="C40" s="4">
-        <f>C2+C6+C9+C19+C35+C39</f>
-        <v/>
-      </c>
-      <c r="D40" s="4">
-        <f>D2+D6+D9+D19+D35+D39</f>
+      <c r="B34" s="4">
+        <f>B2+B6+B9+B19+B29+B33</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>C2+C6+C9+C19+C29+C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>D2+D6+D9+D19+D29+D33</f>
         <v/>
       </c>
     </row>

--- a/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
+++ b/Бюджет/Бюджет строительства — Берта Ромарио.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -481,33 +481,33 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Изыскания, проекты, надзор</t>
+          <t>Коробка и общестроительные работы</t>
         </is>
       </c>
       <c r="B2" s="4">
-        <f>SUM(B3:B5)</f>
+        <f>SUM(B3:B11)</f>
         <v/>
       </c>
       <c r="C2" s="4">
-        <f>SUM(C3:C5)</f>
+        <f>SUM(C3:C11)</f>
         <v/>
       </c>
       <c r="D2" s="4">
-        <f>SUM(D3:D5)</f>
+        <f>SUM(D3:D11)</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Топосъёмка, ГПЗУ, вынос осей</t>
+          <t>Строй Хауз: площадка, фундамент, брус, перекрытие, стропила, кровля, водосток (договор № 26/10-06/1)</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>40</v>
+        <v>43500</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>90</v>
+        <v>43500</v>
       </c>
       <c r="D3" s="6">
         <f>(B3+C3)/2</f>
@@ -517,14 +517,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Оставшиеся проекты (ГП, наружные сети по ТУ, КД6, проект ГСВ) и проверка инженером</t>
+          <t>Окна и витражи ≈ 224–230 м², Schüco / Alutech, с монтажом и опциями</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>250</v>
+        <v>20900</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>600</v>
+        <v>26500</v>
       </c>
       <c r="D4" s="6">
         <f>(B4+C4)/2</f>
@@ -534,14 +534,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Технический надзор заказчика</t>
+          <t>Входные двери</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D5" s="6">
         <f>(B5+C5)/2</f>
@@ -549,35 +549,33 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Фундамент (КЖ0)</t>
-        </is>
-      </c>
-      <c r="B6" s="4">
-        <f>SUM(B7:B8)</f>
-        <v/>
-      </c>
-      <c r="C6" s="4">
-        <f>SUM(C7:C8)</f>
-        <v/>
-      </c>
-      <c r="D6" s="4">
-        <f>SUM(D7:D8)</f>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Защитное покрытие бруса снаружи (в течение 30 дней после сборки — условие гарантии), цоколь</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D6" s="6">
+        <f>(B6+C6)/2</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Сваи забивные 200×200 L=4 м с забивкой</t>
+          <t>Каркасные перегородки (КД6)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="D7" s="6">
         <f>(B7+C7)/2</f>
@@ -587,14 +585,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Плита 250 мм: бетон, арматура, опалубка, XPS, гидроизоляция, работа, прогрев</t>
+          <t>Стяжка с тёплым полом 1 этажа ≈ 210 м²</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1900</v>
+        <v>270</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2700</v>
+        <v>460</v>
       </c>
       <c r="D8" s="6">
         <f>(B8+C8)/2</f>
@@ -602,35 +600,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Коробка дома</t>
-        </is>
-      </c>
-      <c r="B9" s="4">
-        <f>SUM(B10:B18)</f>
-        <v/>
-      </c>
-      <c r="C9" s="4">
-        <f>SUM(C10:C18)</f>
-        <v/>
-      </c>
-      <c r="D9" s="4">
-        <f>SUM(D10:D18)</f>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Лестница, схема Б: металлокаркас + бетон, отделка, ограждение</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>850</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D9" s="6">
+        <f>(B9+C9)/2</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Домокомплект из клееного бруса 240 мм (КД1–КД3)</t>
+          <t>Камин дровяной с дымоходом и подводом воздуха</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>13000</v>
+        <v>400</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18000</v>
+        <v>1200</v>
       </c>
       <c r="D10" s="6">
         <f>(B10+C10)/2</f>
@@ -640,14 +636,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Сборка домокомплекта</t>
+          <t>Отмостка</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3700</v>
+        <v>900</v>
       </c>
       <c r="D11" s="6">
         <f>(B11+C11)/2</f>
@@ -655,33 +651,35 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Перекрытия: двутавровые балки, утепление, ГВЛ, фанера, ЦПС (КД4)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D12" s="6">
-        <f>(B12+C12)/2</f>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Инженерные системы</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>SUM(B13:B22)</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>SUM(C13:C22)</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>SUM(D13:D22)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Кровля: стропила, утеплитель, ОСП, фальц, водосток, снегозадержатели (КД5)</t>
+          <t>Вентиляция и кондиционирование, увлажнение</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3000</v>
+        <v>6670</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4600</v>
+        <v>11530</v>
       </c>
       <c r="D13" s="6">
         <f>(B13+C13)/2</f>
@@ -691,14 +689,14 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Каркасные перегородки (КД6)</t>
+          <t>Отопление и котельная (пеллеты + электро)</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>800</v>
+        <v>4160</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1400</v>
+        <v>8370</v>
       </c>
       <c r="D14" s="6">
         <f>(B14+C14)/2</f>
@@ -708,14 +706,14 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Окна и витражи ≈ 229 м² (2-камерные энергосберегающие) с монтажом</t>
+          <t>Водопровод и канализация (без сантехприборов)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5700</v>
+        <v>1180</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>9200</v>
+        <v>2380</v>
       </c>
       <c r="D15" s="6">
         <f>(B15+C15)/2</f>
@@ -725,14 +723,14 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Входные двери</t>
+          <t>Электрика, свет Maytoni (−50 %), батарея и генератор</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>300</v>
+        <v>6080</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>800</v>
+        <v>11780</v>
       </c>
       <c r="D16" s="6">
         <f>(B16+C16)/2</f>
@@ -742,14 +740,14 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Лестница</t>
+          <t>Сеть, умный дом HA, камеры, домофон, охрана, базовое аудио</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>800</v>
+        <v>2040</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2000</v>
+        <v>4910</v>
       </c>
       <c r="D17" s="6">
         <f>(B17+C17)/2</f>
@@ -759,14 +757,14 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Фасад: шлифовка, покраска бруса, подшивка, цоколь</t>
+          <t>Аудио и кинозона сверх базового (5.1, экран/проектор)</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="D18" s="6">
         <f>(B18+C18)/2</f>
@@ -774,35 +772,33 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Инженерные системы (по разделам РД, см. «Бюджет по разделам РД»)</t>
-        </is>
-      </c>
-      <c r="B19" s="4">
-        <f>SUM(B20:B28)</f>
-        <v/>
-      </c>
-      <c r="C19" s="4">
-        <f>SUM(C20:C28)</f>
-        <v/>
-      </c>
-      <c r="D19" s="4">
-        <f>SUM(D20:D28)</f>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Приводы штор и карнизы 12–15 шт.</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="D19" s="6">
+        <f>(B19+C19)/2</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>291-ОВК Вентиляция и кондиционирование</t>
+          <t>Программирование и пусконаладка умного дома (интегратор)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4840</v>
+        <v>400</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8060</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="6">
         <f>(B20+C20)/2</f>
@@ -812,14 +808,14 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>291-ОВ Отопление, тёплые полы, котельная</t>
+          <t>Молниезащита, заземление, пожарная сигнализация</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>5730</v>
+        <v>620</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>10900</v>
+        <v>1220</v>
       </c>
       <c r="D21" s="6">
         <f>(B21+C21)/2</f>
@@ -829,14 +825,14 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>291-ВК Водоснабжение и канализация (внутренние)</t>
+          <t>Наружные сети и подключения (вода, канализация, кабель, дренаж)</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>1030</v>
+        <v>880</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>2050</v>
+        <v>2270</v>
       </c>
       <c r="D22" s="6">
         <f>(B22+C22)/2</f>
@@ -844,33 +840,35 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>291-ЭОМ Электрооборудование и освещение</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>2620</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>6210</v>
-      </c>
-      <c r="D23" s="6">
-        <f>(B23+C23)/2</f>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Проекты, надзор, стройплощадка</t>
+        </is>
+      </c>
+      <c r="B23" s="4">
+        <f>SUM(B24:B25)</f>
+        <v/>
+      </c>
+      <c r="C23" s="4">
+        <f>SUM(C24:C25)</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>SUM(D24:D25)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>291-СС Слаботочные системы</t>
+          <t>Проектирование инженерии (тендер) и технадзор</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>860</v>
+        <v>750</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>2140</v>
+        <v>1800</v>
       </c>
       <c r="D24" s="6">
         <f>(B24+C24)/2</f>
@@ -880,14 +878,14 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>291-МЗ.ПС Молниезащита, заземление, пожарная сигнализация</t>
+          <t>Стройплощадка вне договора: электроэнергия 15 кВт, вода, охрана, дизель</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1040</v>
+        <v>800</v>
       </c>
       <c r="D25" s="6">
         <f>(B25+C25)/2</f>
@@ -895,33 +893,35 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>291-НС Наружные сети (предварительно)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>980</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>2470</v>
-      </c>
-      <c r="D26" s="6">
-        <f>(B26+C26)/2</f>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>После чистовой (отделка, сантехника, участок, газ 2028)</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <f>SUM(B27:B30)</f>
+        <v/>
+      </c>
+      <c r="C26" s="4">
+        <f>SUM(C27:C30)</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>SUM(D27:D30)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Газ, этап 2: конденсационный котёл, газопровод по участку, проект ГСВ, датчик метана</t>
+          <t>Чистовая отделка: полы, плитка, покраска бруса внутри, потолки, межкомнатные двери</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>540</v>
+        <v>8800</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1400</v>
+        <v>19500</v>
       </c>
       <c r="D27" s="6">
         <f>(B27+C27)/2</f>
@@ -931,7 +931,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Сантехнические приборы (по дизайн-проекту)</t>
+          <t>Сантехприборы по дизайн-проекту</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
@@ -946,35 +946,33 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Отделка и участок</t>
-        </is>
-      </c>
-      <c r="B29" s="4">
-        <f>SUM(B30:B32)</f>
-        <v/>
-      </c>
-      <c r="C29" s="4">
-        <f>SUM(C30:C32)</f>
-        <v/>
-      </c>
-      <c r="D29" s="4">
-        <f>SUM(D30:D32)</f>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Газ, этап 2 (2028): котёл, газопровод по участку, проект</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>480</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D29" s="6">
+        <f>(B29+C29)/2</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Внутренняя отделка (полы, плитка, покраска, потолки, двери)</t>
+          <t>Благоустройство: дорожки, настилы, озеленение, забор и ворота</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>8800</v>
+        <v>1300</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>19500</v>
+        <v>4500</v>
       </c>
       <c r="D30" s="6">
         <f>(B30+C30)/2</f>
@@ -984,14 +982,16 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Благоустройство: отмостка, дорожки, озеленение (ливнёвка — в 291-НС)</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>4500</v>
+          <t>Непредвиденные расходы 10–15 % (кроме договора СХ)</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>ROUND(0.10*(B2+B12+B23+B26-43500),-1)</f>
+        <v/>
+      </c>
+      <c r="C31" s="6">
+        <f>ROUND(0.15*(C2+C12+C23+C26-43500),-1)</f>
+        <v/>
       </c>
       <c r="D31" s="6">
         <f>(B31+C31)/2</f>
@@ -999,57 +999,21 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Временные сооружения, вывоз мусора, охрана</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>400</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>800</v>
-      </c>
-      <c r="D32" s="6">
-        <f>(B32+C32)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Непредвиденные расходы 7 %</t>
-        </is>
-      </c>
-      <c r="B33" s="6">
-        <f>ROUND(0.07*(B2+B6+B9+B19+B29),-1)</f>
-        <v/>
-      </c>
-      <c r="C33" s="6">
-        <f>ROUND(0.07*(C2+C6+C9+C19+C29),-1)</f>
-        <v/>
-      </c>
-      <c r="D33" s="6">
-        <f>ROUND(0.07*(D2+D6+D9+D19+D29),-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B34" s="4">
-        <f>B2+B6+B9+B19+B29+B33</f>
-        <v/>
-      </c>
-      <c r="C34" s="4">
-        <f>C2+C6+C9+C19+C29+C33</f>
-        <v/>
-      </c>
-      <c r="D34" s="4">
-        <f>D2+D6+D9+D19+D29+D33</f>
+      <c r="B32" s="4">
+        <f>B2+B12+B23+B26+B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="4">
+        <f>C2+C12+C23+C26+C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>D2+D12+D23+D26+D31</f>
         <v/>
       </c>
     </row>
